--- a/output/pdf_financials_xlsx/PPM.xlsx
+++ b/output/pdf_financials_xlsx/PPM.xlsx
@@ -1282,46 +1282,46 @@
         <v>-0.161326</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.37793</v>
+        <v>-0.37793</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.566367</v>
+        <v>-0.566367</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.51</v>
+        <v>-0.51</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.192156</v>
+        <v>-0.192156</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.092858</v>
+        <v>-0.092858</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.304437</v>
+        <v>-0.304437</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.190715</v>
+        <v>-0.190715</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.276918</v>
+        <v>-0.276918</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.094777</v>
+        <v>-0.094777</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.528607</v>
+        <v>-0.528607</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.181169</v>
+        <v>-0.181169</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.265144</v>
+        <v>-0.265144</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.080258</v>
+        <v>-0.080258</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.043533</v>
+        <v>-0.043533</v>
       </c>
     </row>
     <row r="17">
@@ -1582,46 +1582,46 @@
         <v>-0.161326</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.37793</v>
+        <v>-0.37793</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.566367</v>
+        <v>-0.566367</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.51</v>
+        <v>-0.51</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.192156</v>
+        <v>-0.192156</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.092858</v>
+        <v>-0.092858</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.304437</v>
+        <v>-0.304437</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.190715</v>
+        <v>-0.190715</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.276918</v>
+        <v>-0.276918</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.094777</v>
+        <v>-0.094777</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.528607</v>
+        <v>-0.528607</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.181169</v>
+        <v>-0.181169</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.265144</v>
+        <v>-0.265144</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.080258</v>
+        <v>-0.080258</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.043533</v>
+        <v>-0.043533</v>
       </c>
     </row>
     <row r="21">
@@ -1756,46 +1756,46 @@
         <v>-0.161326</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.37793</v>
+        <v>-0.37793</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.566367</v>
+        <v>-0.566367</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.51</v>
+        <v>-0.51</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.192156</v>
+        <v>-0.192156</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.092858</v>
+        <v>-0.092858</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.304437</v>
+        <v>-0.304437</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.190715</v>
+        <v>-0.190715</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.276918</v>
+        <v>-0.276918</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.094777</v>
+        <v>-0.094777</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.528607</v>
+        <v>-0.528607</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>0.181169</v>
+        <v>-0.181169</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.265144</v>
+        <v>-0.265144</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>0.080258</v>
+        <v>-0.080258</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>0.043533</v>
+        <v>-0.043533</v>
       </c>
     </row>
     <row r="24">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-18.8965</v>
+        <v>18.8965</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-28.31835</v>
+        <v>28.31835</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-25.5</v>
+        <v>25.5</v>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
@@ -2048,46 +2048,46 @@
         <v>-0.161326</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.37793</v>
+        <v>-0.37793</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.566367</v>
+        <v>-0.566367</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.51</v>
+        <v>-0.51</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.192156</v>
+        <v>-0.192156</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.092858</v>
+        <v>-0.092858</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.304437</v>
+        <v>-0.304437</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.190715</v>
+        <v>-0.190715</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.276918</v>
+        <v>-0.276918</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.094777</v>
+        <v>-0.094777</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.528607</v>
+        <v>-0.528607</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.181169</v>
+        <v>-0.181169</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.265144</v>
+        <v>-0.265144</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>0.080258</v>
+        <v>-0.080258</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>0.043533</v>
+        <v>-0.043533</v>
       </c>
     </row>
     <row r="28">
@@ -2164,46 +2164,46 @@
         <v>-0.161326</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.378283</v>
+        <v>-0.377577</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.566673</v>
+        <v>-0.566061</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.510273</v>
+        <v>-0.509727</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.192523</v>
+        <v>-0.191789</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.09329</v>
+        <v>-0.09242599999999999</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.30474</v>
+        <v>-0.304134</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.190926</v>
+        <v>-0.190504</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.277066</v>
+        <v>-0.27677</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.095123</v>
+        <v>-0.094431</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.528607</v>
+        <v>-0.528607</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.181169</v>
+        <v>-0.181169</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.265144</v>
+        <v>-0.265144</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.080258</v>
+        <v>-0.080258</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>0.043533</v>
+        <v>-0.043533</v>
       </c>
     </row>
     <row r="30">
@@ -2314,46 +2314,46 @@
         <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -28256,31 +28256,31 @@
         </is>
       </c>
       <c r="M199" s="5" t="n">
-        <v>0.304437</v>
+        <v>-0.304437</v>
       </c>
       <c r="N199" s="5" t="n">
-        <v>0.190715</v>
+        <v>-0.190715</v>
       </c>
       <c r="O199" s="5" t="n">
-        <v>0.276918</v>
+        <v>-0.276918</v>
       </c>
       <c r="P199" s="5" t="n">
-        <v>0.094777</v>
+        <v>-0.094777</v>
       </c>
       <c r="Q199" s="5" t="n">
-        <v>0.528607</v>
+        <v>-0.528607</v>
       </c>
       <c r="R199" s="5" t="n">
-        <v>0.181169</v>
+        <v>-0.181169</v>
       </c>
       <c r="S199" s="5" t="n">
-        <v>0.265144</v>
+        <v>-0.265144</v>
       </c>
       <c r="T199" s="5" t="n">
-        <v>0.080258</v>
+        <v>-0.080258</v>
       </c>
       <c r="U199" s="5" t="n">
-        <v>0.043533</v>
+        <v>-0.043533</v>
       </c>
     </row>
     <row r="200">
@@ -33844,10 +33844,10 @@
         </is>
       </c>
       <c r="L256" s="5" t="n">
-        <v>0.092858</v>
+        <v>-0.092858</v>
       </c>
       <c r="M256" s="5" t="n">
-        <v>0.304437</v>
+        <v>-0.304437</v>
       </c>
       <c r="N256" t="inlineStr">
         <is>
@@ -34528,16 +34528,16 @@
         </is>
       </c>
       <c r="I263" s="5" t="n">
-        <v>0.566367</v>
+        <v>-0.566367</v>
       </c>
       <c r="J263" s="5" t="n">
-        <v>0.51</v>
+        <v>-0.51</v>
       </c>
       <c r="K263" s="5" t="n">
-        <v>0.192156</v>
+        <v>-0.192156</v>
       </c>
       <c r="L263" s="5" t="n">
-        <v>0.092858</v>
+        <v>-0.092858</v>
       </c>
       <c r="M263" t="inlineStr">
         <is>
@@ -35824,10 +35824,10 @@
         </is>
       </c>
       <c r="H276" s="5" t="n">
-        <v>0.37793</v>
+        <v>-0.37793</v>
       </c>
       <c r="I276" s="5" t="n">
-        <v>0.566367</v>
+        <v>-0.566367</v>
       </c>
       <c r="J276" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/PPM.xlsx
+++ b/output/pdf_financials_xlsx/PPM.xlsx
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000635</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -1050,40 +1050,40 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000577</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001958</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002423</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000513</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-9.6e-05</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-3.5e-05</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000508</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001848</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000749</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000314</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000216</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001041</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>0</v>
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.181169</v>
+        <v>-0.181804</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>0.345648</v>
@@ -2048,40 +2048,40 @@
         <v>-0.161326</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.37793</v>
+        <v>-0.377353</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.566367</v>
+        <v>-0.564409</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.5075769999999999</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.192156</v>
+        <v>-0.191643</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.092858</v>
+        <v>-0.092762</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.304437</v>
+        <v>-0.304402</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.190715</v>
+        <v>-0.190207</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.276918</v>
+        <v>-0.27507</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.094777</v>
+        <v>-0.094028</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.528607</v>
+        <v>-0.528293</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.181169</v>
+        <v>-0.180953</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.265144</v>
+        <v>-0.264103</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>-0.080258</v>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.181169</v>
+        <v>-0.181804</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>0.345648</v>
@@ -2164,40 +2164,40 @@
         <v>-0.161326</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.377577</v>
+        <v>-0.377</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.566061</v>
+        <v>-0.564103</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.509727</v>
+        <v>-0.507304</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.191789</v>
+        <v>-0.191276</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.09242599999999999</v>
+        <v>-0.09233</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.304134</v>
+        <v>-0.304099</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.190504</v>
+        <v>-0.189996</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.27677</v>
+        <v>-0.274922</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.094431</v>
+        <v>-0.093682</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.528607</v>
+        <v>-0.528293</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.181169</v>
+        <v>-0.180953</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.265144</v>
+        <v>-0.264103</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>-0.080258</v>
@@ -2477,40 +2477,40 @@
         <v>0.334641</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.269796</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.135169</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.046304</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.095985</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.496685</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.227074</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.126326</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.299881</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.06471399999999999</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.011481</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.019259</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.013098</v>
       </c>
     </row>
     <row r="35">
@@ -2593,40 +2593,40 @@
         <v>0.334641</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.269796</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.135169</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.046304</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.095985</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.496685</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.227074</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.126326</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.299881</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.06471399999999999</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.011481</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.019259</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.013098</v>
       </c>
     </row>
     <row r="37">
@@ -3289,22 +3289,22 @@
         <v>0.01748</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.308642</v>
+        <v>0.038846</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.136307</v>
+        <v>0.001138</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.047489</v>
+        <v>0.001185</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.098607</v>
+        <v>0.002622</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.498033</v>
+        <v>0.001348</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.228452</v>
+        <v>0.001378</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0</v>
@@ -8677,7 +8677,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10820,7 +10820,11 @@
           <t>Reclamation deposit 3</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -11289,7 +11293,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17239,7 +17243,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -19930,7 +19938,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -29649,7 +29661,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -33712,7 +33724,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E255" s="5" t="n">

--- a/output/pdf_financials_xlsx/PPM.xlsx
+++ b/output/pdf_financials_xlsx/PPM.xlsx
@@ -6485,37 +6485,37 @@
         <v>0</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>0.002206</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>0.001266</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001123</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000318</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003374</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002541</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0</v>
+        <v>-0.009894999999999999</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>0</v>
+        <v>-0.006878</v>
       </c>
       <c r="P101" s="3" t="n">
-        <v>0</v>
+        <v>0.013355</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002923</v>
       </c>
       <c r="R101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002102</v>
       </c>
     </row>
     <row r="102">
@@ -6775,37 +6775,37 @@
         <v>-0.185827</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.014921</v>
+        <v>0.017127</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.002861</v>
+        <v>0.004127</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.002828</v>
+        <v>0.001705</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>-0.002662</v>
+        <v>-0.00298</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0.000497</v>
+        <v>-0.002877</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>-0.002597</v>
+        <v>-0.005138</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0.059097</v>
+        <v>0.049202</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>-0.035271</v>
+        <v>-0.042149</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>0.105056</v>
+        <v>0.118411</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0.026459</v>
+        <v>0.023536</v>
       </c>
       <c r="R106" s="3" t="n">
-        <v>0.023394</v>
+        <v>0.021292</v>
       </c>
     </row>
     <row r="107">
@@ -7050,7 +7050,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001256</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -7059,13 +7059,13 @@
         <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000393</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00117</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001256</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -8435,13 +8435,13 @@
         <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000393</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00117</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>0</v>
@@ -8484,7 +8484,7 @@
         <v>-0.17112</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.114409</v>
+        <v>-0.115665</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-0.145108</v>
@@ -8493,13 +8493,13 @@
         <v>-0.289337</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-0.400841</v>
+        <v>-0.401234</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>-0.628881</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-0.159162</v>
+        <v>-0.160332</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>-0.088865</v>
@@ -10584,10 +10584,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M22" s="5" t="n">
+        <v>0.10298</v>
       </c>
       <c r="N22" s="5" t="n">
         <v>0.500364</v>
@@ -14988,7 +14986,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -18437,7 +18439,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -18813,7 +18819,11 @@
           <t>Private placements</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -19837,7 +19847,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -21564,7 +21578,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -23691,7 +23709,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -26238,7 +26260,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
